--- a/RFQ Generator Beta Version/Templates/SC TEMPLATE.xlsx
+++ b/RFQ Generator Beta Version/Templates/SC TEMPLATE.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\source\repos\RFQ Generator Beta Version\RFQ Generator Beta Version\bin\Debug\Templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\source\repos\RFQ Generator Beta Version\RFQ Generator Beta Version\Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12F99E80-73E4-46A3-8742-22DCC262EEDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7044D838-49C4-4ECF-BD88-F3AB1B3677B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{38E1F2AF-99C1-49A7-9BAE-E35C28FB0484}"/>
   </bookViews>
@@ -17,7 +17,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'PRICED (2)'!$A$1:$F$41</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="0">'PRICED (2)'!$1:$16</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'PRICED (2)'!$1:$15</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
   <si>
     <t>DESCRIPTION</t>
   </si>
@@ -51,9 +51,6 @@
     <t>AMOUNT (RM)</t>
   </si>
   <si>
-    <t>TERMS</t>
-  </si>
-  <si>
     <t>30 DAYS</t>
   </si>
   <si>
@@ -165,9 +162,6 @@
     <t>_validity</t>
   </si>
   <si>
-    <t>delivery_time</t>
-  </si>
-  <si>
     <t>delivery_term</t>
   </si>
   <si>
@@ -178,6 +172,9 @@
   </si>
   <si>
     <t>delivery_point</t>
+  </si>
+  <si>
+    <t>header_delivery_time</t>
   </si>
 </sst>
 </file>
@@ -390,41 +387,6 @@
         <color indexed="64"/>
       </right>
       <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
       <bottom style="double">
         <color indexed="64"/>
       </bottom>
@@ -460,14 +422,49 @@
       <diagonal/>
     </border>
     <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right style="thin">
         <color indexed="64"/>
       </right>
-      <top style="medium">
+      <top style="thin">
         <color indexed="64"/>
       </top>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -475,7 +472,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -519,12 +516,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -533,21 +524,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="15" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -579,21 +555,12 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -621,13 +588,10 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="4" fontId="4" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -636,28 +600,52 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -760,8 +748,8 @@
       <xdr:rowOff>60960</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>1280160</xdr:colOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>205740</xdr:colOff>
       <xdr:row>37</xdr:row>
       <xdr:rowOff>91440</xdr:rowOff>
     </xdr:to>
@@ -1116,14 +1104,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A661B18-1D6D-4207-BFB0-C1B0C54DD5A6}">
-  <dimension ref="A2:N53"/>
+  <dimension ref="A2:M53"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="11.33203125" style="33" customWidth="1"/>
-    <col min="2" max="2" width="52.6640625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="16.109375" style="4" customWidth="1"/>
-    <col min="4" max="4" width="21.5546875" style="4" customWidth="1"/>
-    <col min="5" max="5" width="1.33203125" style="4" customWidth="1"/>
+    <col min="1" max="1" width="11.33203125" style="26" customWidth="1"/>
+    <col min="2" max="2" width="58.88671875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="18.109375" style="4" customWidth="1"/>
+    <col min="4" max="4" width="15" style="4" customWidth="1"/>
+    <col min="5" max="5" width="0.6640625" style="4" customWidth="1"/>
     <col min="6" max="6" width="14.6640625" style="4" customWidth="1"/>
     <col min="7" max="10" width="9.109375" style="1"/>
     <col min="11" max="11" width="19.109375" style="1" customWidth="1"/>
@@ -1134,15 +1122,15 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:13" ht="68.25" customHeight="1">
-      <c r="C2" s="64" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" s="64"/>
-      <c r="E2" s="64"/>
-      <c r="F2" s="64"/>
+      <c r="C2" s="65" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="65"/>
+      <c r="E2" s="65"/>
+      <c r="F2" s="65"/>
     </row>
     <row r="3" spans="1:13" ht="8.25" customHeight="1">
-      <c r="A3" s="34"/>
+      <c r="A3" s="27"/>
       <c r="B3" s="2"/>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
@@ -1150,118 +1138,118 @@
       <c r="F3" s="3"/>
     </row>
     <row r="5" spans="1:13" ht="15.6">
-      <c r="A5" s="35" t="s">
+      <c r="A5" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="49" t="s">
+        <v>32</v>
+      </c>
+      <c r="D5" s="66" t="s">
+        <v>38</v>
+      </c>
+      <c r="E5" s="66"/>
+      <c r="F5" s="66"/>
+    </row>
+    <row r="6" spans="1:13" ht="15.6">
+      <c r="A6" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="30" t="s">
+      <c r="C6" s="49" t="s">
+        <v>33</v>
+      </c>
+      <c r="D6" s="66" t="s">
+        <v>39</v>
+      </c>
+      <c r="E6" s="66"/>
+      <c r="F6" s="66"/>
+    </row>
+    <row r="7" spans="1:13" ht="15.6">
+      <c r="A7" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="49" t="s">
+        <v>34</v>
+      </c>
+      <c r="D7" s="66" t="s">
+        <v>45</v>
+      </c>
+      <c r="E7" s="66"/>
+      <c r="F7" s="66"/>
+    </row>
+    <row r="8" spans="1:13" ht="15.6">
+      <c r="A8" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="60" t="s">
-        <v>33</v>
-      </c>
-      <c r="D5" s="65" t="s">
-        <v>39</v>
-      </c>
-      <c r="E5" s="65"/>
-      <c r="F5" s="65"/>
-    </row>
-    <row r="6" spans="1:13" ht="15.6">
-      <c r="A6" s="35" t="s">
-        <v>18</v>
-      </c>
-      <c r="C6" s="60" t="s">
-        <v>34</v>
-      </c>
-      <c r="D6" s="65" t="s">
+      <c r="C8" s="49" t="s">
+        <v>35</v>
+      </c>
+      <c r="D8" s="66" t="s">
+        <v>4</v>
+      </c>
+      <c r="E8" s="66"/>
+      <c r="F8" s="66"/>
+    </row>
+    <row r="9" spans="1:13" ht="15.6">
+      <c r="A9" s="29"/>
+      <c r="B9" s="34"/>
+      <c r="C9" s="49" t="s">
+        <v>36</v>
+      </c>
+      <c r="D9" s="51" t="s">
+        <v>41</v>
+      </c>
+      <c r="E9" s="51"/>
+      <c r="F9" s="51"/>
+    </row>
+    <row r="10" spans="1:13" ht="15.6">
+      <c r="A10" s="29"/>
+      <c r="B10" s="34"/>
+      <c r="C10" s="49" t="s">
+        <v>43</v>
+      </c>
+      <c r="D10" s="51" t="s">
+        <v>44</v>
+      </c>
+      <c r="E10" s="51"/>
+      <c r="F10" s="51"/>
+    </row>
+    <row r="11" spans="1:13" ht="15.6">
+      <c r="A11" s="29"/>
+      <c r="B11" s="34"/>
+      <c r="C11" s="49" t="s">
+        <v>37</v>
+      </c>
+      <c r="D11" s="66" t="s">
         <v>40</v>
       </c>
-      <c r="E6" s="65"/>
-      <c r="F6" s="65"/>
-    </row>
-    <row r="7" spans="1:13" ht="15.6">
-      <c r="A7" s="35" t="s">
-        <v>19</v>
-      </c>
-      <c r="C7" s="60" t="s">
-        <v>35</v>
-      </c>
-      <c r="D7" s="65" t="s">
-        <v>42</v>
-      </c>
-      <c r="E7" s="65"/>
-      <c r="F7" s="65"/>
-    </row>
-    <row r="8" spans="1:13" ht="15.6">
-      <c r="A8" s="35" t="s">
-        <v>20</v>
-      </c>
-      <c r="B8" s="35" t="s">
-        <v>22</v>
-      </c>
-      <c r="C8" s="60" t="s">
-        <v>36</v>
-      </c>
-      <c r="D8" s="65" t="s">
-        <v>5</v>
-      </c>
-      <c r="E8" s="65"/>
-      <c r="F8" s="65"/>
-    </row>
-    <row r="9" spans="1:13" ht="15.6">
-      <c r="A9" s="36"/>
-      <c r="B9" s="42"/>
-      <c r="C9" s="60" t="s">
-        <v>37</v>
-      </c>
-      <c r="D9" s="69" t="s">
-        <v>43</v>
-      </c>
-      <c r="E9" s="69"/>
-      <c r="F9" s="69"/>
-    </row>
-    <row r="10" spans="1:13" ht="15.6">
-      <c r="A10" s="36"/>
-      <c r="B10" s="42"/>
-      <c r="C10" s="60" t="s">
-        <v>45</v>
-      </c>
-      <c r="D10" s="69" t="s">
-        <v>46</v>
-      </c>
-      <c r="E10" s="69"/>
-      <c r="F10" s="69"/>
-    </row>
-    <row r="11" spans="1:13" ht="15.6">
-      <c r="A11" s="36"/>
-      <c r="B11" s="42"/>
-      <c r="C11" s="60" t="s">
-        <v>38</v>
-      </c>
-      <c r="D11" s="65" t="s">
-        <v>41</v>
-      </c>
-      <c r="E11" s="65"/>
-      <c r="F11" s="65"/>
+      <c r="E11" s="66"/>
+      <c r="F11" s="66"/>
     </row>
     <row r="12" spans="1:13" ht="22.8">
-      <c r="A12" s="37"/>
-      <c r="B12" s="28" t="s">
-        <v>8</v>
+      <c r="A12" s="30"/>
+      <c r="B12" s="21" t="s">
+        <v>7</v>
       </c>
       <c r="C12" s="6"/>
     </row>
     <row r="13" spans="1:13">
-      <c r="A13" s="37"/>
+      <c r="A13" s="30"/>
       <c r="C13" s="6"/>
     </row>
     <row r="14" spans="1:13" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A14" s="38"/>
+      <c r="A14" s="31"/>
       <c r="C14" s="7"/>
       <c r="E14" s="7"/>
       <c r="F14" s="7"/>
     </row>
     <row r="15" spans="1:13" s="12" customFormat="1" ht="33.75" customHeight="1" thickBot="1">
-      <c r="A15" s="39"/>
+      <c r="A15" s="32"/>
       <c r="B15" s="9" t="s">
         <v>0</v>
       </c>
@@ -1269,157 +1257,157 @@
         <v>1</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E15" s="10"/>
       <c r="F15" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="J15" s="63"/>
-      <c r="K15" s="63"/>
-      <c r="L15" s="63"/>
-      <c r="M15" s="63"/>
+      <c r="J15" s="60"/>
+      <c r="K15" s="60"/>
+      <c r="L15" s="60"/>
+      <c r="M15" s="60"/>
     </row>
     <row r="16" spans="1:13">
-      <c r="A16" s="40"/>
+      <c r="A16" s="33"/>
       <c r="B16" s="15"/>
       <c r="D16" s="14"/>
       <c r="F16" s="16"/>
-      <c r="J16" s="63"/>
-      <c r="K16" s="63"/>
-      <c r="L16" s="63"/>
-      <c r="M16" s="63"/>
+      <c r="J16" s="60"/>
+      <c r="K16" s="60"/>
+      <c r="L16" s="60"/>
+      <c r="M16" s="60"/>
     </row>
     <row r="17" spans="1:13">
-      <c r="A17" s="32" t="s">
+      <c r="A17" s="25" t="s">
+        <v>22</v>
+      </c>
+      <c r="B17" s="35" t="s">
         <v>23</v>
       </c>
-      <c r="B17" s="43" t="s">
+      <c r="C17" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="D17" s="40" t="s">
         <v>25</v>
       </c>
-      <c r="D17" s="50" t="s">
+      <c r="E17" s="41"/>
+      <c r="F17" s="42" t="s">
         <v>26</v>
-      </c>
-      <c r="E17" s="51"/>
-      <c r="F17" s="52" t="s">
-        <v>27</v>
       </c>
       <c r="J17" s="13"/>
       <c r="K17" s="13"/>
       <c r="L17" s="13"/>
       <c r="M17" s="13"/>
     </row>
-    <row r="18" spans="1:13" ht="14.4" thickBot="1">
-      <c r="A18" s="41"/>
-      <c r="B18" s="18"/>
-      <c r="C18" s="17"/>
-      <c r="D18" s="17"/>
-      <c r="E18" s="44"/>
-      <c r="F18" s="45"/>
+    <row r="18" spans="1:13">
+      <c r="A18" s="57"/>
+      <c r="B18" s="58"/>
+      <c r="C18" s="59"/>
+      <c r="D18" s="52"/>
+      <c r="E18" s="46"/>
+      <c r="F18" s="53"/>
     </row>
     <row r="19" spans="1:13" ht="24.6" customHeight="1">
-      <c r="A19" s="54"/>
-      <c r="B19" s="55"/>
-      <c r="C19" s="56"/>
-      <c r="D19" s="61" t="s">
+      <c r="A19" s="44"/>
+      <c r="B19" s="45"/>
+      <c r="C19" s="46"/>
+      <c r="D19" s="54" t="s">
+        <v>27</v>
+      </c>
+      <c r="E19" s="55"/>
+      <c r="F19" s="56" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" ht="24" customHeight="1">
+      <c r="A20" s="44"/>
+      <c r="B20" s="45"/>
+      <c r="C20" s="46"/>
+      <c r="D20" s="50" t="s">
         <v>28</v>
       </c>
-      <c r="E19" s="56"/>
-      <c r="F19" s="59" t="s">
+      <c r="E20" s="46"/>
+      <c r="F20" s="48" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="20" spans="1:13" ht="24" customHeight="1">
-      <c r="A20" s="54"/>
-      <c r="B20" s="55"/>
-      <c r="C20" s="56"/>
-      <c r="D20" s="61" t="s">
-        <v>29</v>
-      </c>
-      <c r="E20" s="56"/>
-      <c r="F20" s="58" t="s">
+    <row r="21" spans="1:13" s="12" customFormat="1" ht="24.75" customHeight="1" thickBot="1">
+      <c r="A21" s="38"/>
+      <c r="C21" s="17"/>
+      <c r="D21" s="36" t="s">
+        <v>5</v>
+      </c>
+      <c r="E21" s="37"/>
+      <c r="F21" s="47" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="21" spans="1:13" s="12" customFormat="1" ht="24.75" customHeight="1" thickBot="1">
-      <c r="A21" s="48"/>
-      <c r="C21" s="19"/>
-      <c r="D21" s="46" t="s">
-        <v>6</v>
-      </c>
-      <c r="E21" s="47"/>
-      <c r="F21" s="57" t="s">
-        <v>32</v>
-      </c>
-    </row>
     <row r="22" spans="1:13" s="12" customFormat="1" ht="24.75" customHeight="1" thickTop="1">
-      <c r="A22" s="48"/>
-      <c r="C22" s="19"/>
-      <c r="D22" s="49"/>
-      <c r="E22" s="49"/>
-      <c r="F22" s="22"/>
+      <c r="A22" s="38"/>
+      <c r="C22" s="17"/>
+      <c r="D22" s="39"/>
+      <c r="E22" s="39"/>
+      <c r="F22" s="20"/>
     </row>
     <row r="23" spans="1:13" s="12" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A23" s="48"/>
-      <c r="C23" s="19"/>
-      <c r="D23" s="49"/>
-      <c r="E23" s="49"/>
-      <c r="F23" s="22"/>
+      <c r="A23" s="38"/>
+      <c r="C23" s="17"/>
+      <c r="D23" s="39"/>
+      <c r="E23" s="39"/>
+      <c r="F23" s="20"/>
     </row>
     <row r="24" spans="1:13">
-      <c r="A24" s="53" t="s">
-        <v>13</v>
-      </c>
-      <c r="B24" s="54"/>
+      <c r="A24" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="B24" s="44"/>
       <c r="C24" s="5"/>
       <c r="D24" s="1"/>
       <c r="E24" s="5"/>
       <c r="F24" s="5"/>
     </row>
     <row r="25" spans="1:13">
-      <c r="A25" s="53" t="s">
-        <v>14</v>
-      </c>
-      <c r="B25" s="54"/>
+      <c r="A25" s="43" t="s">
+        <v>13</v>
+      </c>
+      <c r="B25" s="44"/>
       <c r="C25" s="5"/>
       <c r="D25" s="1"/>
       <c r="E25" s="5"/>
       <c r="F25" s="5"/>
     </row>
     <row r="26" spans="1:13">
-      <c r="A26" s="53"/>
-      <c r="B26" s="54"/>
+      <c r="A26" s="43"/>
+      <c r="B26" s="44"/>
       <c r="C26" s="5"/>
       <c r="D26" s="1"/>
       <c r="E26" s="5"/>
       <c r="F26" s="5"/>
     </row>
     <row r="27" spans="1:13">
-      <c r="A27" s="53" t="s">
-        <v>15</v>
-      </c>
-      <c r="B27" s="54"/>
+      <c r="A27" s="43" t="s">
+        <v>14</v>
+      </c>
+      <c r="B27" s="44"/>
       <c r="C27" s="5"/>
       <c r="D27" s="1"/>
       <c r="E27" s="5"/>
       <c r="F27" s="5"/>
     </row>
     <row r="28" spans="1:13">
-      <c r="A28" s="53"/>
-      <c r="B28" s="54"/>
+      <c r="A28" s="43"/>
+      <c r="B28" s="44"/>
       <c r="C28" s="5"/>
       <c r="D28" s="1"/>
       <c r="E28" s="5"/>
       <c r="F28" s="5"/>
     </row>
     <row r="29" spans="1:13">
-      <c r="A29" s="53" t="s">
-        <v>16</v>
-      </c>
-      <c r="B29" s="54"/>
+      <c r="A29" s="43" t="s">
+        <v>15</v>
+      </c>
+      <c r="B29" s="44"/>
       <c r="C29" s="5"/>
       <c r="D29" s="1"/>
       <c r="E29" s="5"/>
@@ -1437,7 +1425,7 @@
     </row>
     <row r="32" spans="1:13">
       <c r="D32" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E32" s="5"/>
       <c r="F32" s="5"/>
@@ -1448,98 +1436,74 @@
       <c r="F33" s="5"/>
     </row>
     <row r="34" spans="2:6">
-      <c r="B34" s="31"/>
-      <c r="D34" s="66" t="s">
+      <c r="B34" s="24"/>
+      <c r="D34" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="E34" s="61"/>
+      <c r="F34" s="61"/>
+    </row>
+    <row r="35" spans="2:6">
+      <c r="B35" s="18"/>
+      <c r="D35" s="22"/>
+      <c r="E35" s="22"/>
+      <c r="F35" s="22"/>
+    </row>
+    <row r="36" spans="2:6">
+      <c r="B36" s="18"/>
+      <c r="D36" s="22"/>
+      <c r="E36" s="22"/>
+      <c r="F36" s="22"/>
+    </row>
+    <row r="37" spans="2:6">
+      <c r="B37" s="19"/>
+    </row>
+    <row r="38" spans="2:6">
+      <c r="B38" s="19"/>
+      <c r="D38" s="62" t="s">
+        <v>2</v>
+      </c>
+      <c r="E38" s="62"/>
+      <c r="F38" s="62"/>
+    </row>
+    <row r="39" spans="2:6">
+      <c r="B39" s="19"/>
+      <c r="D39" s="63" t="s">
         <v>10</v>
       </c>
-      <c r="E34" s="66"/>
-      <c r="F34" s="66"/>
-    </row>
-    <row r="35" spans="2:6">
-      <c r="B35" s="20"/>
-      <c r="D35" s="29"/>
-      <c r="E35" s="29"/>
-      <c r="F35" s="29"/>
-    </row>
-    <row r="36" spans="2:6">
-      <c r="B36" s="20"/>
-      <c r="D36" s="29"/>
-      <c r="E36" s="29"/>
-      <c r="F36" s="29"/>
-    </row>
-    <row r="37" spans="2:6">
-      <c r="B37" s="21"/>
-    </row>
-    <row r="38" spans="2:6">
-      <c r="B38" s="21"/>
-      <c r="D38" s="67" t="s">
-        <v>2</v>
-      </c>
-      <c r="E38" s="67"/>
-      <c r="F38" s="67"/>
-    </row>
-    <row r="39" spans="2:6">
-      <c r="B39" s="21"/>
-      <c r="D39" s="68" t="s">
+      <c r="E39" s="63"/>
+      <c r="F39" s="63"/>
+    </row>
+    <row r="40" spans="2:6">
+      <c r="D40" s="64" t="s">
         <v>11</v>
       </c>
-      <c r="E39" s="68"/>
-      <c r="F39" s="68"/>
-    </row>
-    <row r="40" spans="2:6">
-      <c r="D40" s="62" t="s">
-        <v>12</v>
-      </c>
-      <c r="E40" s="62"/>
-      <c r="F40" s="62"/>
+      <c r="E40" s="64"/>
+      <c r="F40" s="64"/>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="63"/>
-      <c r="C43" s="63"/>
-      <c r="D43" s="63"/>
-      <c r="E43" s="63"/>
+      <c r="B43" s="60"/>
+      <c r="C43" s="60"/>
+      <c r="D43" s="60"/>
+      <c r="E43" s="60"/>
     </row>
     <row r="44" spans="2:6">
-      <c r="B44" s="63"/>
-      <c r="C44" s="63"/>
-      <c r="D44" s="63"/>
-      <c r="E44" s="63"/>
+      <c r="B44" s="60"/>
+      <c r="C44" s="60"/>
+      <c r="D44" s="60"/>
+      <c r="E44" s="60"/>
     </row>
     <row r="45" spans="2:6">
-      <c r="B45" s="63"/>
-      <c r="C45" s="63"/>
-      <c r="D45" s="63"/>
-      <c r="E45" s="63"/>
-    </row>
-    <row r="51" spans="11:14" ht="24.9" customHeight="1">
-      <c r="K51" s="22"/>
-      <c r="L51" s="23"/>
-      <c r="M51" s="23"/>
-      <c r="N51" s="22" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="52" spans="11:14" ht="3.9" customHeight="1">
-      <c r="K52" s="24"/>
-      <c r="L52" s="25"/>
-      <c r="M52" s="25"/>
-      <c r="N52" s="24"/>
-    </row>
-    <row r="53" spans="11:14" ht="24.9" customHeight="1">
-      <c r="K53" s="22"/>
-      <c r="L53" s="26"/>
-      <c r="M53" s="27"/>
-      <c r="N53" s="22" t="s">
-        <v>5</v>
-      </c>
-    </row>
+      <c r="B45" s="60"/>
+      <c r="C45" s="60"/>
+      <c r="D45" s="60"/>
+      <c r="E45" s="60"/>
+    </row>
+    <row r="51" ht="24.9" customHeight="1"/>
+    <row r="52" ht="3.9" customHeight="1"/>
+    <row r="53" ht="24.9" customHeight="1"/>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="J15:M15"/>
-    <mergeCell ref="J16:M16"/>
-    <mergeCell ref="D34:F34"/>
-    <mergeCell ref="D38:F38"/>
-    <mergeCell ref="D39:F39"/>
     <mergeCell ref="D40:F40"/>
     <mergeCell ref="B43:E43"/>
     <mergeCell ref="B44:E44"/>
@@ -1550,6 +1514,11 @@
     <mergeCell ref="D7:F7"/>
     <mergeCell ref="D8:F8"/>
     <mergeCell ref="D11:F11"/>
+    <mergeCell ref="J15:M15"/>
+    <mergeCell ref="J16:M16"/>
+    <mergeCell ref="D34:F34"/>
+    <mergeCell ref="D38:F38"/>
+    <mergeCell ref="D39:F39"/>
   </mergeCells>
   <pageMargins left="0.55118110236220474" right="0.70866141732283472" top="0.43307086614173229" bottom="0.62992125984251968" header="0.31496062992125984" footer="0.19685039370078741"/>
   <pageSetup paperSize="9" scale="75" orientation="portrait" horizontalDpi="4294967294" verticalDpi="300" r:id="rId1"/>

--- a/RFQ Generator Beta Version/Templates/SC TEMPLATE.xlsx
+++ b/RFQ Generator Beta Version/Templates/SC TEMPLATE.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\source\repos\RFQ Generator Beta Version\RFQ Generator Beta Version\Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7044D838-49C4-4ECF-BD88-F3AB1B3677B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1437C970-A325-4EE3-840D-2C70AEF5F570}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{38E1F2AF-99C1-49A7-9BAE-E35C28FB0484}"/>
   </bookViews>
@@ -144,9 +144,6 @@
     <t>Delivery:</t>
   </si>
   <si>
-    <t>Payment:</t>
-  </si>
-  <si>
     <t>Delivery Term:</t>
   </si>
   <si>
@@ -175,6 +172,9 @@
   </si>
   <si>
     <t>header_delivery_time</t>
+  </si>
+  <si>
+    <t>Payment Term:</t>
   </si>
 </sst>
 </file>
@@ -314,7 +314,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -428,41 +428,19 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
       <right style="medium">
         <color indexed="64"/>
       </right>
       <top/>
-      <bottom style="thin">
+      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -472,7 +450,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -601,32 +579,17 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -637,14 +600,23 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1122,12 +1094,12 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:13" ht="68.25" customHeight="1">
-      <c r="C2" s="65" t="s">
+      <c r="C2" s="54" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="65"/>
-      <c r="E2" s="65"/>
-      <c r="F2" s="65"/>
+      <c r="D2" s="54"/>
+      <c r="E2" s="54"/>
+      <c r="F2" s="54"/>
     </row>
     <row r="3" spans="1:13" ht="8.25" customHeight="1">
       <c r="A3" s="27"/>
@@ -1147,11 +1119,11 @@
       <c r="C5" s="49" t="s">
         <v>32</v>
       </c>
-      <c r="D5" s="66" t="s">
-        <v>38</v>
-      </c>
-      <c r="E5" s="66"/>
-      <c r="F5" s="66"/>
+      <c r="D5" s="55" t="s">
+        <v>37</v>
+      </c>
+      <c r="E5" s="55"/>
+      <c r="F5" s="55"/>
     </row>
     <row r="6" spans="1:13" ht="15.6">
       <c r="A6" s="28" t="s">
@@ -1160,11 +1132,11 @@
       <c r="C6" s="49" t="s">
         <v>33</v>
       </c>
-      <c r="D6" s="66" t="s">
-        <v>39</v>
-      </c>
-      <c r="E6" s="66"/>
-      <c r="F6" s="66"/>
+      <c r="D6" s="55" t="s">
+        <v>38</v>
+      </c>
+      <c r="E6" s="55"/>
+      <c r="F6" s="55"/>
     </row>
     <row r="7" spans="1:13" ht="15.6">
       <c r="A7" s="28" t="s">
@@ -1173,11 +1145,11 @@
       <c r="C7" s="49" t="s">
         <v>34</v>
       </c>
-      <c r="D7" s="66" t="s">
-        <v>45</v>
-      </c>
-      <c r="E7" s="66"/>
-      <c r="F7" s="66"/>
+      <c r="D7" s="55" t="s">
+        <v>44</v>
+      </c>
+      <c r="E7" s="55"/>
+      <c r="F7" s="55"/>
     </row>
     <row r="8" spans="1:13" ht="15.6">
       <c r="A8" s="28" t="s">
@@ -1187,22 +1159,22 @@
         <v>21</v>
       </c>
       <c r="C8" s="49" t="s">
-        <v>35</v>
-      </c>
-      <c r="D8" s="66" t="s">
+        <v>45</v>
+      </c>
+      <c r="D8" s="55" t="s">
         <v>4</v>
       </c>
-      <c r="E8" s="66"/>
-      <c r="F8" s="66"/>
+      <c r="E8" s="55"/>
+      <c r="F8" s="55"/>
     </row>
     <row r="9" spans="1:13" ht="15.6">
       <c r="A9" s="29"/>
       <c r="B9" s="34"/>
       <c r="C9" s="49" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D9" s="51" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E9" s="51"/>
       <c r="F9" s="51"/>
@@ -1211,10 +1183,10 @@
       <c r="A10" s="29"/>
       <c r="B10" s="34"/>
       <c r="C10" s="49" t="s">
+        <v>42</v>
+      </c>
+      <c r="D10" s="51" t="s">
         <v>43</v>
-      </c>
-      <c r="D10" s="51" t="s">
-        <v>44</v>
       </c>
       <c r="E10" s="51"/>
       <c r="F10" s="51"/>
@@ -1223,13 +1195,13 @@
       <c r="A11" s="29"/>
       <c r="B11" s="34"/>
       <c r="C11" s="49" t="s">
-        <v>37</v>
-      </c>
-      <c r="D11" s="66" t="s">
-        <v>40</v>
-      </c>
-      <c r="E11" s="66"/>
-      <c r="F11" s="66"/>
+        <v>36</v>
+      </c>
+      <c r="D11" s="55" t="s">
+        <v>39</v>
+      </c>
+      <c r="E11" s="55"/>
+      <c r="F11" s="55"/>
     </row>
     <row r="12" spans="1:13" ht="22.8">
       <c r="A12" s="30"/>
@@ -1257,26 +1229,26 @@
         <v>1</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E15" s="10"/>
       <c r="F15" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="J15" s="60"/>
-      <c r="K15" s="60"/>
-      <c r="L15" s="60"/>
-      <c r="M15" s="60"/>
+      <c r="J15" s="53"/>
+      <c r="K15" s="53"/>
+      <c r="L15" s="53"/>
+      <c r="M15" s="53"/>
     </row>
     <row r="16" spans="1:13">
       <c r="A16" s="33"/>
       <c r="B16" s="15"/>
       <c r="D16" s="14"/>
       <c r="F16" s="16"/>
-      <c r="J16" s="60"/>
-      <c r="K16" s="60"/>
-      <c r="L16" s="60"/>
-      <c r="M16" s="60"/>
+      <c r="J16" s="53"/>
+      <c r="K16" s="53"/>
+      <c r="L16" s="53"/>
+      <c r="M16" s="53"/>
     </row>
     <row r="17" spans="1:13">
       <c r="A17" s="25" t="s">
@@ -1300,23 +1272,23 @@
       <c r="L17" s="13"/>
       <c r="M17" s="13"/>
     </row>
-    <row r="18" spans="1:13">
-      <c r="A18" s="57"/>
-      <c r="B18" s="58"/>
-      <c r="C18" s="59"/>
-      <c r="D18" s="52"/>
-      <c r="E18" s="46"/>
-      <c r="F18" s="53"/>
+    <row r="18" spans="1:13" ht="14.4" thickBot="1">
+      <c r="A18" s="60"/>
+      <c r="B18" s="61"/>
+      <c r="C18" s="62"/>
+      <c r="D18" s="62"/>
+      <c r="E18" s="63"/>
+      <c r="F18" s="64"/>
     </row>
     <row r="19" spans="1:13" ht="24.6" customHeight="1">
       <c r="A19" s="44"/>
       <c r="B19" s="45"/>
       <c r="C19" s="46"/>
-      <c r="D19" s="54" t="s">
+      <c r="D19" s="50" t="s">
         <v>27</v>
       </c>
-      <c r="E19" s="55"/>
-      <c r="F19" s="56" t="s">
+      <c r="E19" s="59"/>
+      <c r="F19" s="48" t="s">
         <v>29</v>
       </c>
     </row>
@@ -1437,11 +1409,11 @@
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="24"/>
-      <c r="D34" s="61" t="s">
+      <c r="D34" s="56" t="s">
         <v>9</v>
       </c>
-      <c r="E34" s="61"/>
-      <c r="F34" s="61"/>
+      <c r="E34" s="56"/>
+      <c r="F34" s="56"/>
     </row>
     <row r="35" spans="2:6">
       <c r="B35" s="18"/>
@@ -1460,50 +1432,55 @@
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="19"/>
-      <c r="D38" s="62" t="s">
+      <c r="D38" s="57" t="s">
         <v>2</v>
       </c>
-      <c r="E38" s="62"/>
-      <c r="F38" s="62"/>
+      <c r="E38" s="57"/>
+      <c r="F38" s="57"/>
     </row>
     <row r="39" spans="2:6">
       <c r="B39" s="19"/>
-      <c r="D39" s="63" t="s">
+      <c r="D39" s="58" t="s">
         <v>10</v>
       </c>
-      <c r="E39" s="63"/>
-      <c r="F39" s="63"/>
+      <c r="E39" s="58"/>
+      <c r="F39" s="58"/>
     </row>
     <row r="40" spans="2:6">
-      <c r="D40" s="64" t="s">
+      <c r="D40" s="52" t="s">
         <v>11</v>
       </c>
-      <c r="E40" s="64"/>
-      <c r="F40" s="64"/>
+      <c r="E40" s="52"/>
+      <c r="F40" s="52"/>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="60"/>
-      <c r="C43" s="60"/>
-      <c r="D43" s="60"/>
-      <c r="E43" s="60"/>
+      <c r="B43" s="53"/>
+      <c r="C43" s="53"/>
+      <c r="D43" s="53"/>
+      <c r="E43" s="53"/>
     </row>
     <row r="44" spans="2:6">
-      <c r="B44" s="60"/>
-      <c r="C44" s="60"/>
-      <c r="D44" s="60"/>
-      <c r="E44" s="60"/>
+      <c r="B44" s="53"/>
+      <c r="C44" s="53"/>
+      <c r="D44" s="53"/>
+      <c r="E44" s="53"/>
     </row>
     <row r="45" spans="2:6">
-      <c r="B45" s="60"/>
-      <c r="C45" s="60"/>
-      <c r="D45" s="60"/>
-      <c r="E45" s="60"/>
+      <c r="B45" s="53"/>
+      <c r="C45" s="53"/>
+      <c r="D45" s="53"/>
+      <c r="E45" s="53"/>
     </row>
     <row r="51" ht="24.9" customHeight="1"/>
     <row r="52" ht="3.9" customHeight="1"/>
     <row r="53" ht="24.9" customHeight="1"/>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="J15:M15"/>
+    <mergeCell ref="J16:M16"/>
+    <mergeCell ref="D34:F34"/>
+    <mergeCell ref="D38:F38"/>
+    <mergeCell ref="D39:F39"/>
     <mergeCell ref="D40:F40"/>
     <mergeCell ref="B43:E43"/>
     <mergeCell ref="B44:E44"/>
@@ -1514,11 +1491,6 @@
     <mergeCell ref="D7:F7"/>
     <mergeCell ref="D8:F8"/>
     <mergeCell ref="D11:F11"/>
-    <mergeCell ref="J15:M15"/>
-    <mergeCell ref="J16:M16"/>
-    <mergeCell ref="D34:F34"/>
-    <mergeCell ref="D38:F38"/>
-    <mergeCell ref="D39:F39"/>
   </mergeCells>
   <pageMargins left="0.55118110236220474" right="0.70866141732283472" top="0.43307086614173229" bottom="0.62992125984251968" header="0.31496062992125984" footer="0.19685039370078741"/>
   <pageSetup paperSize="9" scale="75" orientation="portrait" horizontalDpi="4294967294" verticalDpi="300" r:id="rId1"/>

--- a/RFQ Generator Beta Version/Templates/SC TEMPLATE.xlsx
+++ b/RFQ Generator Beta Version/Templates/SC TEMPLATE.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\source\repos\RFQ Generator Beta Version\RFQ Generator Beta Version\Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1437C970-A325-4EE3-840D-2C70AEF5F570}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFA0C971-5ED7-4EE3-8320-CCAE933C383A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{38E1F2AF-99C1-49A7-9BAE-E35C28FB0484}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="PRICED (2)" sheetId="14" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'PRICED (2)'!$A$1:$F$41</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'PRICED (2)'!$A$1:$F$39</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'PRICED (2)'!$1:$15</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
   <si>
     <t>DESCRIPTION</t>
   </si>
@@ -54,9 +54,6 @@
     <t>30 DAYS</t>
   </si>
   <si>
-    <t>TOTAL (RM)</t>
-  </si>
-  <si>
     <t>QUOTATION</t>
   </si>
   <si>
@@ -120,21 +117,9 @@
     <t>total_price</t>
   </si>
   <si>
-    <t>SUB TOTAL</t>
-  </si>
-  <si>
-    <t>DISCOUNT</t>
-  </si>
-  <si>
     <t>sub_total</t>
   </si>
   <si>
-    <t>_discount</t>
-  </si>
-  <si>
-    <t>summary_total_price</t>
-  </si>
-  <si>
     <t>Our Ref:</t>
   </si>
   <si>
@@ -175,6 +160,9 @@
   </si>
   <si>
     <t>Payment Term:</t>
+  </si>
+  <si>
+    <t>TOTAL</t>
   </si>
 </sst>
 </file>
@@ -314,7 +302,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -387,7 +375,18 @@
         <color indexed="64"/>
       </right>
       <top/>
-      <bottom style="double">
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -395,8 +394,10 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="double">
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -406,40 +407,9 @@
       <right style="thin">
         <color indexed="64"/>
       </right>
-      <top/>
-      <bottom style="double">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
@@ -450,7 +420,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -535,12 +505,6 @@
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -566,57 +530,54 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="4" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -716,13 +677,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>91440</xdr:colOff>
-      <xdr:row>34</xdr:row>
+      <xdr:row>32</xdr:row>
       <xdr:rowOff>60960</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>205740</xdr:colOff>
-      <xdr:row>37</xdr:row>
+      <xdr:row>35</xdr:row>
       <xdr:rowOff>91440</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1076,7 +1037,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A661B18-1D6D-4207-BFB0-C1B0C54DD5A6}">
-  <dimension ref="A2:M53"/>
+  <dimension ref="A2:M51"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="11.33203125" style="26" customWidth="1"/>
@@ -1094,12 +1055,12 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:13" ht="68.25" customHeight="1">
-      <c r="C2" s="54" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="54"/>
-      <c r="E2" s="54"/>
-      <c r="F2" s="54"/>
+      <c r="C2" s="57" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="57"/>
+      <c r="E2" s="57"/>
+      <c r="F2" s="57"/>
     </row>
     <row r="3" spans="1:13" ht="8.25" customHeight="1">
       <c r="A3" s="27"/>
@@ -1111,102 +1072,102 @@
     </row>
     <row r="5" spans="1:13" ht="15.6">
       <c r="A5" s="28" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B5" s="23" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5" s="49" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" s="45" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" s="58" t="s">
         <v>32</v>
       </c>
-      <c r="D5" s="55" t="s">
-        <v>37</v>
-      </c>
-      <c r="E5" s="55"/>
-      <c r="F5" s="55"/>
+      <c r="E5" s="58"/>
+      <c r="F5" s="58"/>
     </row>
     <row r="6" spans="1:13" ht="15.6">
       <c r="A6" s="28" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" s="49" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="45" t="s">
+        <v>28</v>
+      </c>
+      <c r="D6" s="58" t="s">
         <v>33</v>
       </c>
-      <c r="D6" s="55" t="s">
-        <v>38</v>
-      </c>
-      <c r="E6" s="55"/>
-      <c r="F6" s="55"/>
+      <c r="E6" s="58"/>
+      <c r="F6" s="58"/>
     </row>
     <row r="7" spans="1:13" ht="15.6">
       <c r="A7" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7" s="49" t="s">
-        <v>34</v>
-      </c>
-      <c r="D7" s="55" t="s">
-        <v>44</v>
-      </c>
-      <c r="E7" s="55"/>
-      <c r="F7" s="55"/>
+        <v>17</v>
+      </c>
+      <c r="C7" s="45" t="s">
+        <v>29</v>
+      </c>
+      <c r="D7" s="58" t="s">
+        <v>39</v>
+      </c>
+      <c r="E7" s="58"/>
+      <c r="F7" s="58"/>
     </row>
     <row r="8" spans="1:13" ht="15.6">
       <c r="A8" s="28" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B8" s="28" t="s">
-        <v>21</v>
-      </c>
-      <c r="C8" s="49" t="s">
-        <v>45</v>
-      </c>
-      <c r="D8" s="55" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="45" t="s">
+        <v>40</v>
+      </c>
+      <c r="D8" s="58" t="s">
         <v>4</v>
       </c>
-      <c r="E8" s="55"/>
-      <c r="F8" s="55"/>
+      <c r="E8" s="58"/>
+      <c r="F8" s="58"/>
     </row>
     <row r="9" spans="1:13" ht="15.6">
       <c r="A9" s="29"/>
       <c r="B9" s="34"/>
-      <c r="C9" s="49" t="s">
+      <c r="C9" s="45" t="s">
+        <v>30</v>
+      </c>
+      <c r="D9" s="46" t="s">
         <v>35</v>
       </c>
-      <c r="D9" s="51" t="s">
-        <v>40</v>
-      </c>
-      <c r="E9" s="51"/>
-      <c r="F9" s="51"/>
+      <c r="E9" s="46"/>
+      <c r="F9" s="46"/>
     </row>
     <row r="10" spans="1:13" ht="15.6">
       <c r="A10" s="29"/>
       <c r="B10" s="34"/>
-      <c r="C10" s="49" t="s">
-        <v>42</v>
-      </c>
-      <c r="D10" s="51" t="s">
-        <v>43</v>
-      </c>
-      <c r="E10" s="51"/>
-      <c r="F10" s="51"/>
+      <c r="C10" s="45" t="s">
+        <v>37</v>
+      </c>
+      <c r="D10" s="46" t="s">
+        <v>38</v>
+      </c>
+      <c r="E10" s="46"/>
+      <c r="F10" s="46"/>
     </row>
     <row r="11" spans="1:13" ht="15.6">
       <c r="A11" s="29"/>
       <c r="B11" s="34"/>
-      <c r="C11" s="49" t="s">
-        <v>36</v>
-      </c>
-      <c r="D11" s="55" t="s">
-        <v>39</v>
-      </c>
-      <c r="E11" s="55"/>
-      <c r="F11" s="55"/>
+      <c r="C11" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="D11" s="58" t="s">
+        <v>34</v>
+      </c>
+      <c r="E11" s="58"/>
+      <c r="F11" s="58"/>
     </row>
     <row r="12" spans="1:13" ht="22.8">
       <c r="A12" s="30"/>
       <c r="B12" s="21" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C12" s="6"/>
     </row>
@@ -1229,43 +1190,43 @@
         <v>1</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="E15" s="10"/>
       <c r="F15" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="J15" s="53"/>
-      <c r="K15" s="53"/>
-      <c r="L15" s="53"/>
-      <c r="M15" s="53"/>
+      <c r="J15" s="52"/>
+      <c r="K15" s="52"/>
+      <c r="L15" s="52"/>
+      <c r="M15" s="52"/>
     </row>
     <row r="16" spans="1:13">
       <c r="A16" s="33"/>
       <c r="B16" s="15"/>
       <c r="D16" s="14"/>
       <c r="F16" s="16"/>
-      <c r="J16" s="53"/>
-      <c r="K16" s="53"/>
-      <c r="L16" s="53"/>
-      <c r="M16" s="53"/>
+      <c r="J16" s="52"/>
+      <c r="K16" s="52"/>
+      <c r="L16" s="52"/>
+      <c r="M16" s="52"/>
     </row>
     <row r="17" spans="1:13">
       <c r="A17" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="B17" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="B17" s="35" t="s">
+      <c r="C17" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="D17" s="38" t="s">
         <v>24</v>
       </c>
-      <c r="D17" s="40" t="s">
+      <c r="E17" s="39"/>
+      <c r="F17" s="40" t="s">
         <v>25</v>
-      </c>
-      <c r="E17" s="41"/>
-      <c r="F17" s="42" t="s">
-        <v>26</v>
       </c>
       <c r="J17" s="13"/>
       <c r="K17" s="13"/>
@@ -1273,120 +1234,109 @@
       <c r="M17" s="13"/>
     </row>
     <row r="18" spans="1:13" ht="14.4" thickBot="1">
-      <c r="A18" s="60"/>
-      <c r="B18" s="61"/>
-      <c r="C18" s="62"/>
-      <c r="D18" s="62"/>
-      <c r="E18" s="63"/>
-      <c r="F18" s="64"/>
-    </row>
-    <row r="19" spans="1:13" ht="24.6" customHeight="1">
-      <c r="A19" s="44"/>
-      <c r="B19" s="45"/>
-      <c r="C19" s="46"/>
-      <c r="D19" s="50" t="s">
-        <v>27</v>
+      <c r="A18" s="47"/>
+      <c r="B18" s="48"/>
+      <c r="C18" s="49"/>
+      <c r="D18" s="49"/>
+      <c r="E18" s="50"/>
+      <c r="F18" s="51"/>
+    </row>
+    <row r="19" spans="1:13" ht="24.6" customHeight="1" thickBot="1">
+      <c r="A19" s="42"/>
+      <c r="B19" s="43"/>
+      <c r="C19" s="44"/>
+      <c r="D19" s="61" t="s">
+        <v>41</v>
       </c>
       <c r="E19" s="59"/>
-      <c r="F19" s="48" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" ht="24" customHeight="1">
-      <c r="A20" s="44"/>
-      <c r="B20" s="45"/>
-      <c r="C20" s="46"/>
-      <c r="D20" s="50" t="s">
-        <v>28</v>
-      </c>
-      <c r="E20" s="46"/>
-      <c r="F20" s="48" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" s="12" customFormat="1" ht="24.75" customHeight="1" thickBot="1">
-      <c r="A21" s="38"/>
+      <c r="F19" s="60" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" s="12" customFormat="1" ht="24.75" customHeight="1">
+      <c r="A20" s="36"/>
+      <c r="C20" s="17"/>
+      <c r="D20" s="37"/>
+      <c r="E20" s="37"/>
+      <c r="F20" s="20"/>
+    </row>
+    <row r="21" spans="1:13" s="12" customFormat="1" ht="24.75" customHeight="1">
+      <c r="A21" s="36"/>
       <c r="C21" s="17"/>
-      <c r="D21" s="36" t="s">
-        <v>5</v>
-      </c>
+      <c r="D21" s="37"/>
       <c r="E21" s="37"/>
-      <c r="F21" s="47" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" s="12" customFormat="1" ht="24.75" customHeight="1" thickTop="1">
-      <c r="A22" s="38"/>
-      <c r="C22" s="17"/>
-      <c r="D22" s="39"/>
-      <c r="E22" s="39"/>
-      <c r="F22" s="20"/>
-    </row>
-    <row r="23" spans="1:13" s="12" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A23" s="38"/>
-      <c r="C23" s="17"/>
-      <c r="D23" s="39"/>
-      <c r="E23" s="39"/>
-      <c r="F23" s="20"/>
+      <c r="F21" s="20"/>
+    </row>
+    <row r="22" spans="1:13">
+      <c r="A22" s="41" t="s">
+        <v>11</v>
+      </c>
+      <c r="B22" s="42"/>
+      <c r="C22" s="5"/>
+      <c r="D22" s="1"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="5"/>
+    </row>
+    <row r="23" spans="1:13">
+      <c r="A23" s="41" t="s">
+        <v>12</v>
+      </c>
+      <c r="B23" s="42"/>
+      <c r="C23" s="5"/>
+      <c r="D23" s="1"/>
+      <c r="E23" s="5"/>
+      <c r="F23" s="5"/>
     </row>
     <row r="24" spans="1:13">
-      <c r="A24" s="43" t="s">
-        <v>12</v>
-      </c>
-      <c r="B24" s="44"/>
+      <c r="A24" s="41"/>
+      <c r="B24" s="42"/>
       <c r="C24" s="5"/>
       <c r="D24" s="1"/>
       <c r="E24" s="5"/>
       <c r="F24" s="5"/>
     </row>
     <row r="25" spans="1:13">
-      <c r="A25" s="43" t="s">
+      <c r="A25" s="41" t="s">
         <v>13</v>
       </c>
-      <c r="B25" s="44"/>
+      <c r="B25" s="42"/>
       <c r="C25" s="5"/>
       <c r="D25" s="1"/>
       <c r="E25" s="5"/>
       <c r="F25" s="5"/>
     </row>
     <row r="26" spans="1:13">
-      <c r="A26" s="43"/>
-      <c r="B26" s="44"/>
+      <c r="A26" s="41"/>
+      <c r="B26" s="42"/>
       <c r="C26" s="5"/>
       <c r="D26" s="1"/>
       <c r="E26" s="5"/>
       <c r="F26" s="5"/>
     </row>
     <row r="27" spans="1:13">
-      <c r="A27" s="43" t="s">
+      <c r="A27" s="41" t="s">
         <v>14</v>
       </c>
-      <c r="B27" s="44"/>
+      <c r="B27" s="42"/>
       <c r="C27" s="5"/>
       <c r="D27" s="1"/>
       <c r="E27" s="5"/>
       <c r="F27" s="5"/>
     </row>
     <row r="28" spans="1:13">
-      <c r="A28" s="43"/>
-      <c r="B28" s="44"/>
-      <c r="C28" s="5"/>
-      <c r="D28" s="1"/>
+      <c r="D28" s="5"/>
       <c r="E28" s="5"/>
       <c r="F28" s="5"/>
     </row>
     <row r="29" spans="1:13">
-      <c r="A29" s="43" t="s">
-        <v>15</v>
-      </c>
-      <c r="B29" s="44"/>
-      <c r="C29" s="5"/>
-      <c r="D29" s="1"/>
+      <c r="D29" s="5"/>
       <c r="E29" s="5"/>
       <c r="F29" s="5"/>
     </row>
     <row r="30" spans="1:13">
-      <c r="D30" s="5"/>
+      <c r="D30" s="5" t="s">
+        <v>7</v>
+      </c>
       <c r="E30" s="5"/>
       <c r="F30" s="5"/>
     </row>
@@ -1396,101 +1346,89 @@
       <c r="F31" s="5"/>
     </row>
     <row r="32" spans="1:13">
-      <c r="D32" s="5" t="s">
+      <c r="B32" s="24"/>
+      <c r="D32" s="53" t="s">
         <v>8</v>
       </c>
-      <c r="E32" s="5"/>
-      <c r="F32" s="5"/>
+      <c r="E32" s="53"/>
+      <c r="F32" s="53"/>
     </row>
     <row r="33" spans="2:6">
-      <c r="D33" s="5"/>
-      <c r="E33" s="5"/>
-      <c r="F33" s="5"/>
+      <c r="B33" s="18"/>
+      <c r="D33" s="22"/>
+      <c r="E33" s="22"/>
+      <c r="F33" s="22"/>
     </row>
     <row r="34" spans="2:6">
-      <c r="B34" s="24"/>
-      <c r="D34" s="56" t="s">
-        <v>9</v>
-      </c>
-      <c r="E34" s="56"/>
-      <c r="F34" s="56"/>
+      <c r="B34" s="18"/>
+      <c r="D34" s="22"/>
+      <c r="E34" s="22"/>
+      <c r="F34" s="22"/>
     </row>
     <row r="35" spans="2:6">
-      <c r="B35" s="18"/>
-      <c r="D35" s="22"/>
-      <c r="E35" s="22"/>
-      <c r="F35" s="22"/>
+      <c r="B35" s="19"/>
     </row>
     <row r="36" spans="2:6">
-      <c r="B36" s="18"/>
-      <c r="D36" s="22"/>
-      <c r="E36" s="22"/>
-      <c r="F36" s="22"/>
+      <c r="B36" s="19"/>
+      <c r="D36" s="54" t="s">
+        <v>2</v>
+      </c>
+      <c r="E36" s="54"/>
+      <c r="F36" s="54"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="19"/>
+      <c r="D37" s="55" t="s">
+        <v>9</v>
+      </c>
+      <c r="E37" s="55"/>
+      <c r="F37" s="55"/>
     </row>
     <row r="38" spans="2:6">
-      <c r="B38" s="19"/>
-      <c r="D38" s="57" t="s">
-        <v>2</v>
-      </c>
-      <c r="E38" s="57"/>
-      <c r="F38" s="57"/>
-    </row>
-    <row r="39" spans="2:6">
-      <c r="B39" s="19"/>
-      <c r="D39" s="58" t="s">
+      <c r="D38" s="56" t="s">
         <v>10</v>
       </c>
-      <c r="E39" s="58"/>
-      <c r="F39" s="58"/>
-    </row>
-    <row r="40" spans="2:6">
-      <c r="D40" s="52" t="s">
-        <v>11</v>
-      </c>
-      <c r="E40" s="52"/>
-      <c r="F40" s="52"/>
+      <c r="E38" s="56"/>
+      <c r="F38" s="56"/>
+    </row>
+    <row r="41" spans="2:6">
+      <c r="B41" s="52"/>
+      <c r="C41" s="52"/>
+      <c r="D41" s="52"/>
+      <c r="E41" s="52"/>
+    </row>
+    <row r="42" spans="2:6">
+      <c r="B42" s="52"/>
+      <c r="C42" s="52"/>
+      <c r="D42" s="52"/>
+      <c r="E42" s="52"/>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="53"/>
-      <c r="C43" s="53"/>
-      <c r="D43" s="53"/>
-      <c r="E43" s="53"/>
-    </row>
-    <row r="44" spans="2:6">
-      <c r="B44" s="53"/>
-      <c r="C44" s="53"/>
-      <c r="D44" s="53"/>
-      <c r="E44" s="53"/>
-    </row>
-    <row r="45" spans="2:6">
-      <c r="B45" s="53"/>
-      <c r="C45" s="53"/>
-      <c r="D45" s="53"/>
-      <c r="E45" s="53"/>
-    </row>
+      <c r="B43" s="52"/>
+      <c r="C43" s="52"/>
+      <c r="D43" s="52"/>
+      <c r="E43" s="52"/>
+    </row>
+    <row r="49" ht="24.9" customHeight="1"/>
+    <row r="50" ht="3.9" customHeight="1"/>
     <row r="51" ht="24.9" customHeight="1"/>
-    <row r="52" ht="3.9" customHeight="1"/>
-    <row r="53" ht="24.9" customHeight="1"/>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="J15:M15"/>
-    <mergeCell ref="J16:M16"/>
-    <mergeCell ref="D34:F34"/>
     <mergeCell ref="D38:F38"/>
-    <mergeCell ref="D39:F39"/>
-    <mergeCell ref="D40:F40"/>
+    <mergeCell ref="B41:E41"/>
+    <mergeCell ref="B42:E42"/>
     <mergeCell ref="B43:E43"/>
-    <mergeCell ref="B44:E44"/>
-    <mergeCell ref="B45:E45"/>
     <mergeCell ref="C2:F2"/>
     <mergeCell ref="D5:F5"/>
     <mergeCell ref="D6:F6"/>
     <mergeCell ref="D7:F7"/>
     <mergeCell ref="D8:F8"/>
     <mergeCell ref="D11:F11"/>
+    <mergeCell ref="J15:M15"/>
+    <mergeCell ref="J16:M16"/>
+    <mergeCell ref="D32:F32"/>
+    <mergeCell ref="D36:F36"/>
+    <mergeCell ref="D37:F37"/>
   </mergeCells>
   <pageMargins left="0.55118110236220474" right="0.70866141732283472" top="0.43307086614173229" bottom="0.62992125984251968" header="0.31496062992125984" footer="0.19685039370078741"/>
   <pageSetup paperSize="9" scale="75" orientation="portrait" horizontalDpi="4294967294" verticalDpi="300" r:id="rId1"/>
